--- a/in_piura_plantillas/salida/Plantilla_Excel_Bloque_86_IN_Piura.xlsx
+++ b/in_piura_plantillas/salida/Plantilla_Excel_Bloque_86_IN_Piura.xlsx
@@ -2305,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2732,31 +2732,39 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>ALCANCE DE LOS PROMEDIOS. La fila TOTAL / PROMEDIO omite las celdas «Por determinar»: los promedios de PENDIENTE y MSAVI 2024 se calculan sobre 4 de los 9 bloques de la microcuenca; los 5 bloques restantes carecen de dato derivado del MDE. Los totales de ÁREA y % de microcuenca sí comprenden la totalidad de los 9 bloques. No se estima ningún valor ausente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>LECTURA INTRAMICROCUENCA. El bloque 86 ocupa el puesto 5 de 9 por superficie dentro de la microcuenca C1081-Q9583 (7.54 % de las 398.04 ha preliminares de la microcuenca). El cuadro conserva todos los bloques catalogados en la microcuenca, incluidos los descartados en el tamizaje, para referencia del conjunto. Los bloques sin ficha DT figuran con sus parámetros de gabinete.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>NOTA METODOLÓGICA. Área y MSAVI 2024 proceden del catálogo maestro de bloques V5/V6. El rango altitudinal y la pendiente promedio proceden del reporte de estadística zonal sobre el MDE («Rango de altitud y Pendiente Promedio por Bloques V6»). El porcentaje de «Vegetación alta» procede de la estadística zonal del NDVI mediana 2025 (Sentinel-2). Los totales y promedios se calculan con fórmulas sobre las filas del cuadro.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/in_piura_plantillas/salida/Plantilla_Excel_Bloque_86_IN_Piura.xlsx
+++ b/in_piura_plantillas/salida/Plantilla_Excel_Bloque_86_IN_Piura.xlsx
@@ -120,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -142,11 +142,55 @@
         <color rgb="009C9C9C"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009C9C9C"/>
+      </right>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009C9C9C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009C9C9C"/>
+      </right>
+      <top style="thin">
+        <color rgb="009C9C9C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009C9C9C"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,6 +301,8 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -622,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -675,6 +721,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -868,6 +915,7 @@
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -1033,6 +1081,7 @@
       <c r="E25" s="8" t="n"/>
       <c r="F25" s="8" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
@@ -1070,7 +1119,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>BAJO umbral 0.4976</t>
+          <t>Bajo umbral · distribución areal: 99.87 % del bloque BAJO el umbral (29.962 ha de 30.001 ha)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1089,96 +1138,95 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Superficie clasificada NDVI 2025 (ha)</t>
+          <t>MSAVI 2024 — superficie BAJO el umbral 0.4976 (ha)</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>30.01</v>
+        <v>29.962</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Desviación frente al catálogo (%)</t>
+          <t>MSAVI 2024 — % del bloque BAJO el umbral</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.03</v>
+        <v>99.87</v>
       </c>
       <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>MSAVI 2024 — clase areal dominante</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Suelo desnudo / no vegetal</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>MSAVI 2024 — fuente de la distribución areal</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Conteo de celdas sobre la cartografía MSAVI 2024 del bloque (MSAVI Bloque 86.png)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Superficie clasificada NDVI 2025 (ha)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Desviación frente al catálogo (%)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>4. ECOSISTEMA Y ESTADO DE CONSERVACIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Tipo de ecosistema (UP)</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Bosque Estacionalmente Seco de Colina y Montaña (Bes-cm) — asignación POR VERIFICAR</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Superficie de ecosistema (ha)</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>30.01 ha (100% del bloque)</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Estado de conservación</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Alterado (intervención marcada)</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Uso actual dominante del suelo</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Pastoreo extensivo</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Tipo de cobertura dominante</t>
+          <t>Tipo de ecosistema (UP)</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Matorral ralo</t>
+          <t>Bosque Estacionalmente Seco de Colina y Montaña (Bes-cm) — asignación POR VERIFICAR</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Cobertura vegetal total — campo (%)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>24</v>
+          <t>Superficie de ecosistema (ha)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>30.01 ha (100% del bloque)</t>
+        </is>
       </c>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
@@ -1186,20 +1234,22 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Suelo desnudo — campo (%)</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>50</v>
+          <t>Estado de conservación</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Alterado (intervención marcada)</t>
+        </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Regeneración natural</t>
+          <t>Uso actual dominante del suelo</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Escasa (&lt;10 pl./100m²)</t>
+          <t>Pastoreo extensivo</t>
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1208,23 +1258,21 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Nivel general de erosión</t>
+          <t>Tipo de cobertura dominante</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Moderada (surcos)</t>
+          <t>Matorral ralo</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>N.° de cárcavas registradas</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>No inventariadas</t>
-        </is>
+          <t>Cobertura vegetal total — campo (%)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>24</v>
       </c>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
@@ -1232,99 +1280,98 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Elenco florístico (n.° de taxones)</t>
+          <t>Suelo desnudo — campo (%)</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Estado sanitario</t>
+          <t>Regeneración natural</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>En blanco (sin mediciones)</t>
+          <t>Escasa (&lt;10 pl./100m²)</t>
         </is>
       </c>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Nivel general de erosión</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Moderada (surcos)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>N.° de cárcavas registradas</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>No inventariadas</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Elenco florístico (n.° de taxones)</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Estado sanitario</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>En blanco (sin mediciones)</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>5. RESPONSABLE Y MODALIDAD DE LA EVALUACIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Responsable de la evaluación</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Brigada de campo IN Piura — levantamiento fotogramétrico RPA; nominación POR CONFIRMAR según parte diario</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Fecha de evaluación</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Hora de registro</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>11:58 h</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Correlativo de ficha</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>F-DT-01-B86-2026</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Entidad</t>
+          <t>Responsable de la evaluación</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>ANIN - DIME - SESDI</t>
+          <t>Brigada de campo IN Piura — levantamiento fotogramétrico RPA; nominación POR CONFIRMAR según parte diario</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Fase del estudio</t>
+          <t>Fecha de evaluación</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Preinversión (Perfil) · Invierte.pe</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1333,22 +1380,22 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Instrumento aplicado</t>
+          <t>Hora de registro</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Fichas F-DT-01 a F-DT-05 (Plantilla V5)</t>
+          <t>11:58 h</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Parcela de muestreo</t>
+          <t>Correlativo de ficha</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>No instalada — fotointerpretación de ortofoto RPA</t>
+          <t>F-DT-01-B86-2026</t>
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1357,99 +1404,100 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Estaciones fotográficas georreferenciadas</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="n">
-        <v>13</v>
+          <t>Entidad</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>ANIN - DIME - SESDI</t>
+        </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Modalidad de acceso</t>
+          <t>Fase del estudio</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Vehicular 4x4 hasta el bloque</t>
+          <t>Preinversión (Perfil) · Invierte.pe</t>
         </is>
       </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Instrumento aplicado</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Fichas F-DT-01 a F-DT-05 (Plantilla V5)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Parcela de muestreo</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>No instalada — fotointerpretación de ortofoto RPA</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Estaciones fotográficas georreferenciadas</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Modalidad de acceso</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Vehicular 4x4 hasta el bloque</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>6. SÍNTESIS PARA LA GESTIÓN DEL RIESGO EN CONTEXTO DE CAMBIO CLIMÁTICO</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Causa subyacente principal</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Ausencia de régimen de manejo del pastoreo comunal combinada con la presión de expansión de las áreas irrigadas</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Velocidad de degradación</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>EN BLANCO — no se dispone de serie Theil-Sen (TAU) ni de MSAVI multianual</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Reversibilidad técnica</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Parcialmente reversible</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Urgencia de intervención</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Urgencia de control de erosión</t>
+          <t>Causa subyacente principal</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Ausencia de régimen de manejo del pastoreo comunal combinada con la presión de expansión de las áreas irrigadas</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Zona de recarga hídrica</t>
+          <t>Velocidad de degradación</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>EN BLANCO — no se dispone de serie Theil-Sen (TAU) ni de MSAVI multianual</t>
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1458,22 +1506,22 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Peligro integrado preliminar (MCA-AHP)</t>
+          <t>Reversibilidad técnica</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>No disponible en los insumos; debe tomarse del modelamiento de mesolocalización</t>
+          <t>Parcialmente reversible</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Prioridad de intervención</t>
+          <t>Urgencia de intervención</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Por definir en mesolocalización</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1482,49 +1530,103 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Estado de verificación de campo</t>
+          <t>Urgencia de control de erosión</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>VERIFICADO</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Marco del indicador de brecha</t>
+          <t>Zona de recarga hídrica</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>R.M. N.° 00213-2024-MINAM</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Peligro integrado preliminar (MCA-AHP)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>No disponible en los insumos; debe tomarse del modelamiento de mesolocalización</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Prioridad de intervención</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Por definir en mesolocalización</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
     <row r="54" ht="72" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Estado de verificación de campo</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>VERIFICADO</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Marco del indicador de brecha</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>R.M. N.° 00213-2024-MINAM</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>DECLARACIÓN DE INTEGRIDAD DE DATOS. Ningún valor ausente ha sido estimado o inferido sin declararlo. Los campos que no pudieron sustentarse en observación de campo, estadística zonal o catálogo oficial se consignan como «Por determinar» o «Por verificar». La altitud y la pendiente proceden de estadística zonal sobre el modelo digital de elevación; el MSAVI 2024 y el NDVI mediana 2025 proceden de compuestos Sentinel-2. Las discrepancias detectadas entre campo, gabinete y catálogo se listan en la hoja «Control de consistencia».</t>
         </is>
       </c>
+      <c r="B56" s="38" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="38" t="n"/>
+      <c r="E56" s="38" t="n"/>
+      <c r="F56" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1536,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1588,6 +1690,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -1628,15 +1731,11 @@
           <t>&gt; 0.6139</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1655,15 +1754,11 @@
           <t>0.4976 - 0.6139</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B11" s="20" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0.13</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1682,15 +1777,11 @@
           <t>0.3813 - 0.4976</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B12" s="18" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>4.65</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1709,15 +1800,11 @@
           <t>0.2650 - 0.3813</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B13" s="32" t="n">
+        <v>13.2814</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>44.27</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1736,15 +1823,11 @@
           <t>&lt;= 0.2650</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Por determinar</t>
-        </is>
+      <c r="B14" s="18" t="n">
+        <v>15.2856</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>50.95</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1758,207 +1841,243 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL CLASIFICADO</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>SUM(B10:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="19">
+        <f>SUM(C10:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Suma de las cinco clases MSAVI 2024</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Iguala la superficie de catálogo (V5/V6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>MSAVI 2024 — MEDIA DEL BLOQUE</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>0.273472</v>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Vigor muy bajo · clase 0.2650 - 0.3813</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>BAJO umbral 0.4976</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>NOTA METODOLÓGICA. La media del MSAVI 2024 del bloque (0.273472) procede del catálogo maestro de bloques V5/V6 y es dato oficial. La DISTRIBUCIÓN AREAL por clase de MSAVI no está disponible como estadística zonal en los insumos de este entregable: se consigna «Por determinar» y NO se estima, conforme a la declaración de integridad de datos del proyecto. La fila resaltada indica la clase en la que cae la media del bloque. Para el dimensionamiento de metas físicas debe ejecutarse estadística zonal directa sobre el ráster MSAVI 2024 recortado al polígono.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="17" ht="72" customHeight="1"/>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>NOTA METODOLÓGICA. La media del MSAVI 2024 del bloque procede del catálogo maestro de bloques V5/V6 y es dato oficial. La DISTRIBUCIÓN AREAL por clase se obtuvo por conteo de celdas sobre la cartografía temática MSAVI 2024 del bloque (carpeta Drive «MSAVI BLOQUES V6»), clasificada con la paleta RdYlGn de cinco clases y los mismos umbrales del proyecto. El reparto porcentual es el medido sobre el polígono del bloque; las hectáreas se obtienen aplicando ese reparto a la superficie de catálogo (V5/V6) declarada en la hoja «Resumen», de modo que el total por clase cuadra con la superficie oficial. Umbral de brecha 0.4976 conforme a la R.M. N.° 00213-2024-MINAM. CONTRASTE INDEPENDIENTE: la tabla de intersección vectorial «BLOQUES_V6_INTERSECC_MSAVI» reproduce el mismo ordenamiento de bloques (correlación de Pearson 0.949 sobre el porcentaje bajo umbral en los 117 bloques); no se usa para el metrado porque su campo AREA_M2 conserva el área del polígono padre y no la de cada pieza de intersección. El refrendo por estadística zonal directa sobre el ráster MSAVI 2024 recortado al polígono queda pendiente.</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="39" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1"/>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>B. NDVI MEDIANA 2025 — DISTRIBUCIÓN AREAL (ESTADÍSTICA ZONAL)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Clase NDVI</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Superficie (ha)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>% del área clasificada</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Interpretación</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Vegetación alta</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B22" s="18" t="n">
         <v>0.3153</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C22" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Dosel continuo, matorral denso o mosaico agroforestal</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Vegetación mediana</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B23" s="20" t="n">
         <v>2.6483</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C23" s="21" t="n">
         <v>8.82</v>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Pastizal cultivado, matorral ralo, parcelas agrícolas</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Vegetación ligera</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B24" s="18" t="n">
         <v>20.4961</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C24" s="19" t="n">
         <v>68.3</v>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Cobertura discontinua, suelo parcialmente expuesto</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Tierra desnuda</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B25" s="20" t="n">
         <v>6.5505</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C25" s="21" t="n">
         <v>21.83</v>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Suelo desnudo, afloramientos, plataformas y taludes</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>TOTAL CLASIFICADO</t>
         </is>
       </c>
-      <c r="B25" s="22">
+      <c r="B26" s="22">
         <f>SUM(B21:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="23">
+      <c r="C26" s="23">
         <f>SUM(C21:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr"/>
+      <c r="E26" s="17" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>Superficie de catálogo (V5/V6)</t>
         </is>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B27" s="25" t="n">
         <v>30.001</v>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>Desviación planimétrica frente al catálogo</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>+0.03 %</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="108" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="28" ht="108" customHeight="1"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>LECTURA CRÍTICA. Los índices MSAVI y NDVI miden vigor y densidad de biomasa, no composición ni integridad ecosistémica. Un valor alto NO equivale a ausencia de degradación: en bloques con mosaico agrícola, pastizal cultivado o plantaciones, la respuesta espectral puede ser alta sobre una unidad productora sustituida en su composición. La diferencia entre ambos productos no debe leerse como mejora entre 2024 y 2025: son índices distintos (el NDVI satura ante biomasa densa, el MSAVI conserva sensibilidad al suelo de fondo) aplicados sobre compuestos temporales distintos. Contraste registrado en este bloque: la cobertura vegetal estimada en campo es 24 % frente a un 1.05 % del polígono clasificado como «Vegetación alta» por el NDVI 2025; la observación de campo corresponde a una parcela o recorrido puntual y no es estadísticamente representativa de las 30.001 ha del bloque.</t>
         </is>
       </c>
+      <c r="B29" s="38" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2283,6 +2402,12 @@
           <t>CONTROL GEOMÉTRICO. Las coordenadas de esta hoja proceden de la ficha DT del bloque (F-DT-01 a F-DT-05) y corresponden a rasgos erosivos, fuentes de agua, especies clave y al punto de muestreo declarado. La distancia al centroide se calcula sobre coordenadas UTM 17S y es referencial: no acredita inclusión ni exclusión respecto del polígono, que exige prueba de inclusión sobre la geometría del bloque. Las estaciones situadas a menos de ~30 m del límite deben considerarse SOBRE EL LÍMITE, dentro del margen de error de la georreferenciación (± 10-15 m). ALCANCE DE LA EVIDENCIA. EL BLOQUE 86 NO CUENTA CON FICHAS F-DT-01 A F-DT-05 LEVANTADAS EN CAMPO. La información procede de: (i) levantamiento fotogramétrico con RPA del 14-08-2026, 13 fotogramas cenitales georreferenciados por EXIF sobre el ámbito de los bloques 85-87; (ii) cartografía NDVI mediana 2025 y MSAVI 2024; (iii) imagen Google Earth / Airbus del 09-11-2023 y perfil de elevación sobre transecto oeste-este de 607 m. BLOQUE FUERA DEL CATÁLOGO MAESTRO: no figura en «Bloques V4» ni en Bloques V5; solo en el REPORTE_BLOQUES_V6 y en «Bloques extras». Centroide por restitución cartográfica (E 642 380 / N 9 410 190, ±25 m). PENDIENTE Y ALTITUD: el transecto de 607 m registra cotas de 245 – 287 – 314 msnm, pendiente media 17.8% en el ascenso y −15.0% en el descenso, con máximas de 30.5% y −34.2%. POR VERIFICAR con estadística zonal del DEM. EXPOSICIÓN MIXTA: se consigna «Oeste» por ser el flanco de mayor superficie y el que enfrenta al centro poblado; el análisis de aspecto del DEM deberá confirmarlo. ATENCIÓN: el UTM del punto de registro (645 575 · 9 393 500) es el valor por defecto de la plantilla.</t>
         </is>
       </c>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2738,6 +2863,13 @@
           <t>ALCANCE DE LOS PROMEDIOS. La fila TOTAL / PROMEDIO omite las celdas «Por determinar»: los promedios de PENDIENTE y MSAVI 2024 se calculan sobre 4 de los 9 bloques de la microcuenca; los 5 bloques restantes carecen de dato derivado del MDE. Los totales de ÁREA y % de microcuenca sí comprenden la totalidad de los 9 bloques. No se estima ningún valor ausente.</t>
         </is>
       </c>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="39" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -2745,6 +2877,13 @@
           <t>LECTURA INTRAMICROCUENCA. El bloque 86 ocupa el puesto 5 de 9 por superficie dentro de la microcuenca C1081-Q9583 (7.54 % de las 398.04 ha preliminares de la microcuenca). El cuadro conserva todos los bloques catalogados en la microcuenca, incluidos los descartados en el tamizaje, para referencia del conjunto. Los bloques sin ficha DT figuran con sus parámetros de gabinete.</t>
         </is>
       </c>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="38" t="n"/>
+      <c r="E22" s="38" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="38" t="n"/>
+      <c r="H22" s="39" t="n"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -2752,6 +2891,13 @@
           <t>NOTA METODOLÓGICA. Área y MSAVI 2024 proceden del catálogo maestro de bloques V5/V6. El rango altitudinal y la pendiente promedio proceden del reporte de estadística zonal sobre el MDE («Rango de altitud y Pendiente Promedio por Bloques V6»). El porcentaje de «Vegetación alta» procede de la estadística zonal del NDVI mediana 2025 (Sentinel-2). Los totales y promedios se calculan con fórmulas sobre las filas del cuadro.</t>
         </is>
       </c>
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2776,7 +2922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2828,6 +2974,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -3429,39 +3576,72 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Distribución areal de clases MSAVI 2024</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>La hoja «Cobertura MSAVI-NDVI» consignaba «Por determinar» en la distribución areal de clases MSAVI 2024; se incorpora el metrado por clase medido sobre la cartografía temática MSAVI 2024 del bloque: 99.87 % del bloque (29.962 ha) bajo el umbral 0.4976 y 0.13 % sobre el umbral; clase areal dominante «Suelo desnudo / no vegetal».</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
+        <is>
+          <t>CORREGIDO</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>Se sustituye «Por determinar» por el metrado por clase. Las hectáreas se derivan del reparto porcentual medido aplicado a la superficie de catálogo (V5/V6) del bloque, por lo que la suma de las cinco clases iguala dicha superficie. Pendiente de refrendo con estadística zonal directa sobre el ráster MSAVI 2024 cuando se disponga del insumo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>21 verificaciones</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>CONFORME: 2 · NO SUSTANTIVA: 5 · SUSTANTIVA: 14</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>22 verificaciones</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>CONFORME: 2 · NO SUSTANTIVA: 5 · SUSTANTIVA: 14 · CORREGIDO: 1</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr"/>
+      <c r="E33" s="17" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>NOTA METODOLÓGICA. Este control se genera de forma reproducible cruzando la ficha DT del bloque (F-DT-01 a F-DT-05) con el catálogo maestro de bloques V5/V6, la estadística zonal de altitud y pendiente sobre el MDE, la estadística zonal del NDVI mediana 2025 y el cruce INEI-Bloques de centros poblados. Una calificación CONFORME acredita que la verificación se ejecutó y no arrojó discrepancia; no equivale a validación de campo del dato.</t>
         </is>
       </c>
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="38" t="n"/>
+      <c r="E35" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A3:E3"/>
